--- a/artfynd/A 10555-2026 artfynd.xlsx
+++ b/artfynd/A 10555-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136020385</v>
       </c>
       <c r="B2" t="n">
-        <v>92348</v>
+        <v>92351</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136020391</v>
       </c>
       <c r="B3" t="n">
-        <v>92281</v>
+        <v>92284</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136020384</v>
       </c>
       <c r="B4" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 10555-2026 artfynd.xlsx
+++ b/artfynd/A 10555-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136020385</v>
       </c>
       <c r="B2" t="n">
-        <v>92351</v>
+        <v>92352</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136020391</v>
       </c>
       <c r="B3" t="n">
-        <v>92284</v>
+        <v>92285</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136020384</v>
       </c>
       <c r="B4" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
